--- a/7 Future comparisons/Bonaire/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/7 Future comparisons/Bonaire/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>58.25632227475376</v>
+        <v>56.55550803132954</v>
       </c>
       <c r="C3" t="n">
-        <v>49.67298894142045</v>
+        <v>47.97217469799619</v>
       </c>
       <c r="D3" t="n">
-        <v>6.008595054321576</v>
+        <v>5.949500866651855</v>
       </c>
       <c r="E3" t="n">
-        <v>5.681115549439983</v>
+        <v>4.38361543317958</v>
       </c>
       <c r="F3" t="n">
-        <v>3.004297527160788</v>
+        <v>3.004426958964073</v>
       </c>
       <c r="G3" t="n">
-        <v>35.05013781687586</v>
+        <v>34.70542172213582</v>
       </c>
       <c r="H3" t="n">
-        <v>3.004297527160788</v>
+        <v>3.004426958964073</v>
       </c>
       <c r="I3" t="n">
-        <v>2.50358127263399</v>
+        <v>2.503689132470061</v>
       </c>
       <c r="J3" t="n">
-        <v>3.004297527160788</v>
+        <v>3.004426958964073</v>
       </c>
       <c r="K3" t="n">
-        <v>41.74367772524622</v>
+        <v>43.44449196867047</v>
       </c>
       <c r="L3" t="n">
         <v>8.5</v>
       </c>
       <c r="M3" t="n">
-        <v>99.91666666666667</v>
+        <v>99.91666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58.74953364653417</v>
+        <v>55.55024083808944</v>
       </c>
       <c r="C4" t="n">
-        <v>50.58507694077775</v>
+        <v>47.38543238942318</v>
       </c>
       <c r="D4" t="n">
-        <v>6.010007647470421</v>
+        <v>5.823998517807024</v>
       </c>
       <c r="E4" t="n">
-        <v>6.568783643604733</v>
+        <v>4.639315312048252</v>
       </c>
       <c r="F4" t="n">
-        <v>3.007858036298769</v>
+        <v>3.008193109450789</v>
       </c>
       <c r="G4" t="n">
-        <v>35.05837794357745</v>
+        <v>33.97332468720764</v>
       </c>
       <c r="H4" t="n">
-        <v>3.007858036298769</v>
+        <v>3.008193109450789</v>
       </c>
       <c r="I4" t="n">
-        <v>2.088790302985255</v>
+        <v>2.089022992674159</v>
       </c>
       <c r="J4" t="n">
-        <v>3.007858036298769</v>
+        <v>3.008193109450789</v>
       </c>
       <c r="K4" t="n">
-        <v>41.25046635346584</v>
+        <v>44.44975916191057</v>
       </c>
       <c r="L4" t="n">
-        <v>8.094912781516568</v>
+        <v>8.095261528319863</v>
       </c>
       <c r="M4" t="n">
-        <v>99.93045607576016</v>
+        <v>99.9304530796536</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.43761116000961</v>
+        <v>54.83746313846796</v>
       </c>
       <c r="C5" t="n">
-        <v>51.62321454873034</v>
+        <v>47.02219600920809</v>
       </c>
       <c r="D5" t="n">
-        <v>6.007071018584431</v>
+        <v>5.736650206203555</v>
       </c>
       <c r="E5" t="n">
-        <v>7.614541715651904</v>
+        <v>4.860184308265817</v>
       </c>
       <c r="F5" t="n">
-        <v>3.01079712361015</v>
+        <v>3.01137971923314</v>
       </c>
       <c r="G5" t="n">
-        <v>35.04124760840917</v>
+        <v>33.46379286952073</v>
       </c>
       <c r="H5" t="n">
-        <v>3.01079712361015</v>
+        <v>3.01137971923314</v>
       </c>
       <c r="I5" t="n">
-        <v>1.742359446533651</v>
+        <v>1.742696596778438</v>
       </c>
       <c r="J5" t="n">
-        <v>3.01079712361015</v>
+        <v>3.01137971923314</v>
       </c>
       <c r="K5" t="n">
-        <v>40.56238883999038</v>
+        <v>45.16253686153204</v>
       </c>
       <c r="L5" t="n">
-        <v>7.756374658418583</v>
+        <v>7.75723871279671</v>
       </c>
       <c r="M5" t="n">
-        <v>99.94197804713932</v>
+        <v>99.94197158353683</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.24419704479595</v>
+        <v>53.40607979587741</v>
       </c>
       <c r="C6" t="n">
-        <v>51.72223771861611</v>
+        <v>45.8826649546297</v>
       </c>
       <c r="D6" t="n">
-        <v>5.982030226963237</v>
+        <v>5.555320951102046</v>
       </c>
       <c r="E6" t="n">
-        <v>7.874060837966338</v>
+        <v>4.948819967653884</v>
       </c>
       <c r="F6" t="n">
-        <v>3.013258771120042</v>
+        <v>3.014111764772428</v>
       </c>
       <c r="G6" t="n">
-        <v>34.89517632395221</v>
+        <v>32.4060388814286</v>
       </c>
       <c r="H6" t="n">
-        <v>3.013258771120042</v>
+        <v>3.014111764772428</v>
       </c>
       <c r="I6" t="n">
-        <v>1.453153342554032</v>
+        <v>1.453564701375592</v>
       </c>
       <c r="J6" t="n">
-        <v>3.013258771120042</v>
+        <v>3.014111764772428</v>
       </c>
       <c r="K6" t="n">
-        <v>40.75580295520405</v>
+        <v>46.59392020412258</v>
       </c>
       <c r="L6" t="n">
-        <v>7.473560452665009</v>
+        <v>7.475006602448312</v>
       </c>
       <c r="M6" t="n">
-        <v>99.95160112648517</v>
+        <v>99.9515917612006</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>70.7136020443379</v>
+        <v>66.36008468956405</v>
       </c>
       <c r="C7" t="n">
-        <v>59.76974982393981</v>
+        <v>54.82324986978527</v>
       </c>
       <c r="D7" t="n">
-        <v>5.995479196634201</v>
+        <v>5.570236771948059</v>
       </c>
       <c r="E7" t="n">
-        <v>13.50554488329064</v>
+        <v>11.20763221211841</v>
       </c>
       <c r="F7" t="n">
-        <v>3.020033264776208</v>
+        <v>3.022204537717309</v>
       </c>
       <c r="G7" t="n">
-        <v>37.38306852250916</v>
+        <v>35.1703746431948</v>
       </c>
       <c r="H7" t="n">
-        <v>3.020033264776208</v>
+        <v>3.022204537717309</v>
       </c>
       <c r="I7" t="n">
-        <v>4.769409647575289</v>
+        <v>5.34522744915084</v>
       </c>
       <c r="J7" t="n">
-        <v>3.020033264776208</v>
+        <v>3.022204537717309</v>
       </c>
       <c r="K7" t="n">
-        <v>29.28639795566209</v>
+        <v>33.63991531043595</v>
       </c>
       <c r="L7" t="n">
-        <v>10.78522852110268</v>
+        <v>11.35913768138413</v>
       </c>
       <c r="M7" t="n">
-        <v>99.84137630070458</v>
+        <v>99.82230286160535</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69.45891866083345</v>
+        <v>64.34744130154577</v>
       </c>
       <c r="C8" t="n">
-        <v>59.31186049031342</v>
+        <v>53.70019747823126</v>
       </c>
       <c r="D8" t="n">
-        <v>5.874442579394959</v>
+        <v>5.366811391242883</v>
       </c>
       <c r="E8" t="n">
-        <v>13.89657910116206</v>
+        <v>11.54243850973867</v>
       </c>
       <c r="F8" t="n">
-        <v>3.025804582494838</v>
+        <v>3.029194253731544</v>
       </c>
       <c r="G8" t="n">
-        <v>36.62837986333953</v>
+        <v>33.88595045365835</v>
       </c>
       <c r="H8" t="n">
-        <v>3.025804582494838</v>
+        <v>3.029194253731544</v>
       </c>
       <c r="I8" t="n">
-        <v>3.982103369452399</v>
+        <v>4.464658185711229</v>
       </c>
       <c r="J8" t="n">
-        <v>3.025804582494838</v>
+        <v>3.029194253731544</v>
       </c>
       <c r="K8" t="n">
-        <v>30.54108133916656</v>
+        <v>35.65255869845423</v>
       </c>
       <c r="L8" t="n">
-        <v>10.01457456919849</v>
+        <v>10.49876528306032</v>
       </c>
       <c r="M8" t="n">
-        <v>99.86751639867846</v>
+        <v>99.85152145974581</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75.17167909941449</v>
+        <v>70.86580239092729</v>
       </c>
       <c r="C9" t="n">
-        <v>63.61612688527093</v>
+        <v>58.58864010697204</v>
       </c>
       <c r="D9" t="n">
-        <v>5.883803534057065</v>
+        <v>5.377025790967496</v>
       </c>
       <c r="E9" t="n">
-        <v>16.31698902782157</v>
+        <v>14.28825209396203</v>
       </c>
       <c r="F9" t="n">
-        <v>3.030626217761557</v>
+        <v>3.034959576694375</v>
       </c>
       <c r="G9" t="n">
-        <v>38.48608073316149</v>
+        <v>35.9999116486924</v>
       </c>
       <c r="H9" t="n">
-        <v>4.829959574647098</v>
+        <v>5.08442723585592</v>
       </c>
       <c r="I9" t="n">
-        <v>3.59359379420417</v>
+        <v>4.046266468060686</v>
       </c>
       <c r="J9" t="n">
-        <v>3.030626217761557</v>
+        <v>3.034959576694375</v>
       </c>
       <c r="K9" t="n">
-        <v>24.8283209005855</v>
+        <v>29.13419760907271</v>
       </c>
       <c r="L9" t="n">
-        <v>11.43595633099573</v>
+        <v>12.14254294966781</v>
       </c>
       <c r="M9" t="n">
-        <v>99.88040411685215</v>
+        <v>99.86538066571256</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>75.81282907262697</v>
+        <v>71.93529870497969</v>
       </c>
       <c r="C10" t="n">
-        <v>64.50061191954279</v>
+        <v>59.84397670381257</v>
       </c>
       <c r="D10" t="n">
-        <v>5.854163676097357</v>
+        <v>5.353070740867362</v>
       </c>
       <c r="E10" t="n">
-        <v>17.071881968921</v>
+        <v>15.24934732368179</v>
       </c>
       <c r="F10" t="n">
-        <v>3.034653137215387</v>
+        <v>3.039752143205124</v>
       </c>
       <c r="G10" t="n">
-        <v>38.62561779049276</v>
+        <v>36.29630733910844</v>
       </c>
       <c r="H10" t="n">
-        <v>5.169789325279409</v>
+        <v>5.549234134722176</v>
       </c>
       <c r="I10" t="n">
-        <v>3.022070037405669</v>
+        <v>3.407834880189668</v>
       </c>
       <c r="J10" t="n">
-        <v>3.034653137215387</v>
+        <v>3.039752143205124</v>
       </c>
       <c r="K10" t="n">
-        <v>24.18717092737303</v>
+        <v>28.06470129502032</v>
       </c>
       <c r="L10" t="n">
-        <v>11.21161515923569</v>
+        <v>11.97790660172909</v>
       </c>
       <c r="M10" t="n">
-        <v>99.89939800615151</v>
+        <v>99.88658460056197</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>74.18910672709613</v>
+        <v>70.03202370066457</v>
       </c>
       <c r="C11" t="n">
-        <v>63.38232617683533</v>
+        <v>58.50851294257395</v>
       </c>
       <c r="D11" t="n">
-        <v>5.706188501562803</v>
+        <v>5.181012494763982</v>
       </c>
       <c r="E11" t="n">
-        <v>17.06056494922961</v>
+        <v>15.23315427795483</v>
       </c>
       <c r="F11" t="n">
-        <v>3.038090794922268</v>
+        <v>3.043866528619561</v>
       </c>
       <c r="G11" t="n">
-        <v>37.649281485208</v>
+        <v>35.12967247043036</v>
       </c>
       <c r="H11" t="n">
-        <v>5.175645667112699</v>
+        <v>5.556745170790111</v>
       </c>
       <c r="I11" t="n">
-        <v>2.521244534138473</v>
+        <v>2.84370622948616</v>
       </c>
       <c r="J11" t="n">
-        <v>3.038090794922268</v>
+        <v>3.043866528619561</v>
       </c>
       <c r="K11" t="n">
-        <v>25.81089327290388</v>
+        <v>29.96797629933544</v>
       </c>
       <c r="L11" t="n">
-        <v>10.72283416033286</v>
+        <v>11.42884867808536</v>
       </c>
       <c r="M11" t="n">
-        <v>99.91605361007205</v>
+        <v>99.90533791999474</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>72.17281292706812</v>
+        <v>67.62090042641961</v>
       </c>
       <c r="C12" t="n">
-        <v>61.78800478285835</v>
+        <v>56.57154169606353</v>
       </c>
       <c r="D12" t="n">
-        <v>5.521110627997913</v>
+        <v>4.961904271306263</v>
       </c>
       <c r="E12" t="n">
-        <v>16.85772553305967</v>
+        <v>14.98435587262393</v>
       </c>
       <c r="F12" t="n">
-        <v>3.041041740620698</v>
+        <v>3.047426401622149</v>
       </c>
       <c r="G12" t="n">
-        <v>36.4281425486622</v>
+        <v>33.64401688989926</v>
       </c>
       <c r="H12" t="n">
-        <v>5.180672853707482</v>
+        <v>5.56324391405949</v>
       </c>
       <c r="I12" t="n">
-        <v>2.103077882399456</v>
+        <v>2.372526675286375</v>
       </c>
       <c r="J12" t="n">
-        <v>3.041041740620698</v>
+        <v>3.047426401622149</v>
       </c>
       <c r="K12" t="n">
-        <v>27.82718707293188</v>
+        <v>32.37909957358039</v>
       </c>
       <c r="L12" t="n">
-        <v>10.31477357381703</v>
+        <v>10.97036689064814</v>
       </c>
       <c r="M12" t="n">
-        <v>99.92996542960725</v>
+        <v>99.92100816029206</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>69.25800399315933</v>
+        <v>64.31894908220127</v>
       </c>
       <c r="C13" t="n">
-        <v>59.22530566676496</v>
+        <v>53.66526968502302</v>
       </c>
       <c r="D13" t="n">
-        <v>5.251882867947136</v>
+        <v>4.660953577967902</v>
       </c>
       <c r="E13" t="n">
-        <v>16.32802737564876</v>
+        <v>14.40537644418444</v>
       </c>
       <c r="F13" t="n">
-        <v>3.043609011800897</v>
+        <v>3.050552107513</v>
       </c>
       <c r="G13" t="n">
-        <v>34.65178487681038</v>
+        <v>31.60343132917921</v>
       </c>
       <c r="H13" t="n">
-        <v>5.185046418178401</v>
+        <v>5.568950061471341</v>
       </c>
       <c r="I13" t="n">
-        <v>1.754044430972869</v>
+        <v>1.979133454372386</v>
       </c>
       <c r="J13" t="n">
-        <v>3.043609011800897</v>
+        <v>3.050552107513</v>
       </c>
       <c r="K13" t="n">
-        <v>30.74199600684066</v>
+        <v>35.68105091779874</v>
       </c>
       <c r="L13" t="n">
-        <v>9.974279496327727</v>
+        <v>10.58777587842028</v>
       </c>
       <c r="M13" t="n">
-        <v>99.94158116993336</v>
+        <v>99.93409648124205</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>66.6448566763345</v>
+        <v>61.35937580713205</v>
       </c>
       <c r="C14" t="n">
-        <v>56.90577409746187</v>
+        <v>51.03561983021595</v>
       </c>
       <c r="D14" t="n">
-        <v>5.011486078200614</v>
+        <v>4.392647311217788</v>
       </c>
       <c r="E14" t="n">
-        <v>15.82443277499595</v>
+        <v>13.85126181558383</v>
       </c>
       <c r="F14" t="n">
-        <v>3.045835795006821</v>
+        <v>3.053287750261098</v>
       </c>
       <c r="G14" t="n">
-        <v>33.06565318788557</v>
+        <v>29.78419015147099</v>
       </c>
       <c r="H14" t="n">
-        <v>5.188839932470536</v>
+        <v>5.57394412723821</v>
       </c>
       <c r="I14" t="n">
-        <v>1.462773112768179</v>
+        <v>1.650756901099032</v>
       </c>
       <c r="J14" t="n">
-        <v>3.045835795006821</v>
+        <v>3.053287750261098</v>
       </c>
       <c r="K14" t="n">
-        <v>33.35514332366552</v>
+        <v>38.64062419286795</v>
       </c>
       <c r="L14" t="n">
-        <v>9.690359122456689</v>
+        <v>10.268780047628</v>
       </c>
       <c r="M14" t="n">
-        <v>99.95127654358407</v>
+        <v>99.9450240707119</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>63.32496882217642</v>
+        <v>57.67902404196701</v>
       </c>
       <c r="C15" t="n">
-        <v>53.83068291425981</v>
+        <v>47.63030705518798</v>
       </c>
       <c r="D15" t="n">
-        <v>4.705839790962113</v>
+        <v>4.059269628325505</v>
       </c>
       <c r="E15" t="n">
-        <v>15.06260741170119</v>
+        <v>13.02948171074895</v>
       </c>
       <c r="F15" t="n">
-        <v>3.04779141615516</v>
+        <v>3.055717020618031</v>
       </c>
       <c r="G15" t="n">
-        <v>31.04900703257552</v>
+        <v>27.52373453188067</v>
       </c>
       <c r="H15" t="n">
-        <v>5.192171499170199</v>
+        <v>5.578378893413898</v>
       </c>
       <c r="I15" t="n">
-        <v>1.219760255457084</v>
+        <v>1.376725236361917</v>
       </c>
       <c r="J15" t="n">
-        <v>3.04779141615516</v>
+        <v>3.055717020618031</v>
       </c>
       <c r="K15" t="n">
-        <v>36.67503117782358</v>
+        <v>42.32097595803299</v>
       </c>
       <c r="L15" t="n">
-        <v>9.45365332145084</v>
+        <v>10.00286262841517</v>
       </c>
       <c r="M15" t="n">
-        <v>99.95936741353424</v>
+        <v>99.95414564163613</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>60.66245923078203</v>
+        <v>54.66575345866124</v>
       </c>
       <c r="C16" t="n">
-        <v>51.37214720659084</v>
+        <v>44.84614414665097</v>
       </c>
       <c r="D16" t="n">
-        <v>4.46177594986023</v>
+        <v>3.787743300904264</v>
       </c>
       <c r="E16" t="n">
-        <v>14.45090563084353</v>
+        <v>12.34927965684872</v>
       </c>
       <c r="F16" t="n">
-        <v>3.04949467182738</v>
+        <v>3.057856196492691</v>
       </c>
       <c r="G16" t="n">
-        <v>29.43868023536417</v>
+        <v>25.68265984637336</v>
       </c>
       <c r="H16" t="n">
-        <v>5.195073139850142</v>
+        <v>5.582284076213216</v>
       </c>
       <c r="I16" t="n">
-        <v>1.017034931209188</v>
+        <v>1.148074185336294</v>
       </c>
       <c r="J16" t="n">
-        <v>3.04949467182738</v>
+        <v>3.057856196492691</v>
       </c>
       <c r="K16" t="n">
-        <v>39.33754076921798</v>
+        <v>45.33424654133877</v>
       </c>
       <c r="L16" t="n">
-        <v>9.256429794872929</v>
+        <v>9.781366944333527</v>
       </c>
       <c r="M16" t="n">
-        <v>99.96611777068175</v>
+        <v>99.96175763232327</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>57.33370619485461</v>
+        <v>51.08951012040928</v>
       </c>
       <c r="C17" t="n">
-        <v>48.21335830352474</v>
+        <v>41.46075041033046</v>
       </c>
       <c r="D17" t="n">
-        <v>4.15653130355938</v>
+        <v>3.465994962402584</v>
       </c>
       <c r="E17" t="n">
-        <v>13.60491352858366</v>
+        <v>11.4598293842092</v>
       </c>
       <c r="F17" t="n">
-        <v>3.050998039754585</v>
+        <v>3.05976615507297</v>
       </c>
       <c r="G17" t="n">
-        <v>27.42468409638524</v>
+        <v>23.50105658622063</v>
       </c>
       <c r="H17" t="n">
-        <v>5.197634254781769</v>
+        <v>5.585770810279111</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8479469320353948</v>
+        <v>0.9573260671518091</v>
       </c>
       <c r="J17" t="n">
-        <v>3.050998039754585</v>
+        <v>3.05976615507297</v>
       </c>
       <c r="K17" t="n">
-        <v>42.66629380514539</v>
+        <v>48.91048987959072</v>
       </c>
       <c r="L17" t="n">
-        <v>9.092096921018513</v>
+        <v>9.596868760486151</v>
       </c>
       <c r="M17" t="n">
-        <v>99.97174902968864</v>
+        <v>99.96810905040734</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>54.52348284387925</v>
+        <v>48.05640228653063</v>
       </c>
       <c r="C18" t="n">
-        <v>45.54467402453464</v>
+        <v>38.58650120779782</v>
       </c>
       <c r="D18" t="n">
-        <v>3.898636529235822</v>
+        <v>3.194184821906167</v>
       </c>
       <c r="E18" t="n">
-        <v>12.89030344212694</v>
+        <v>10.69416259930756</v>
       </c>
       <c r="F18" t="n">
-        <v>3.052316637006913</v>
+        <v>3.061460238338942</v>
       </c>
       <c r="G18" t="n">
-        <v>25.72310116595583</v>
+        <v>21.65805751616805</v>
       </c>
       <c r="H18" t="n">
-        <v>5.199880597177818</v>
+        <v>5.588863452127431</v>
       </c>
       <c r="I18" t="n">
-        <v>0.706927835369022</v>
+        <v>0.7982134203435461</v>
       </c>
       <c r="J18" t="n">
-        <v>3.052316637006913</v>
+        <v>3.061460238338942</v>
       </c>
       <c r="K18" t="n">
-        <v>45.47651715612075</v>
+        <v>51.94359771346937</v>
       </c>
       <c r="L18" t="n">
-        <v>8.955254737899184</v>
+        <v>9.44330868797859</v>
       </c>
       <c r="M18" t="n">
-        <v>99.97644591855457</v>
+        <v>99.97340760924578</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>51.65161555455423</v>
+        <v>44.98033891715036</v>
       </c>
       <c r="C19" t="n">
-        <v>42.79067490657951</v>
+        <v>35.64266478138816</v>
       </c>
       <c r="D19" t="n">
-        <v>3.634492730924311</v>
+        <v>2.918669177716877</v>
       </c>
       <c r="E19" t="n">
-        <v>12.13869165304046</v>
+        <v>9.888670446463996</v>
       </c>
       <c r="F19" t="n">
-        <v>3.053477506495934</v>
+        <v>3.062970097916313</v>
       </c>
       <c r="G19" t="n">
-        <v>23.98028733979526</v>
+        <v>19.7899334090305</v>
       </c>
       <c r="H19" t="n">
-        <v>5.201858236934661</v>
+        <v>5.591619783535605</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5893305808676605</v>
+        <v>0.6655059045707544</v>
       </c>
       <c r="J19" t="n">
-        <v>3.053477506495934</v>
+        <v>3.062970097916313</v>
       </c>
       <c r="K19" t="n">
-        <v>48.34838444544578</v>
+        <v>55.01966108284964</v>
       </c>
       <c r="L19" t="n">
-        <v>8.841303763658916</v>
+        <v>9.315501540752662</v>
       </c>
       <c r="M19" t="n">
-        <v>99.98036311568421</v>
+        <v>99.97782740499045</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>49.33468115505472</v>
+        <v>42.50338527300671</v>
       </c>
       <c r="C20" t="n">
-        <v>40.5718663003214</v>
+        <v>33.27572086261885</v>
       </c>
       <c r="D20" t="n">
-        <v>3.421323083507753</v>
+        <v>2.697074564799242</v>
       </c>
       <c r="E20" t="n">
-        <v>11.53571962101809</v>
+        <v>9.241403594398752</v>
       </c>
       <c r="F20" t="n">
-        <v>3.054491051432191</v>
+        <v>3.064302875191801</v>
       </c>
       <c r="G20" t="n">
-        <v>22.57379961905304</v>
+        <v>18.28741895246907</v>
       </c>
       <c r="H20" t="n">
-        <v>5.20358489680491</v>
+        <v>5.594052841496483</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4912718318065444</v>
+        <v>0.5548295694595562</v>
       </c>
       <c r="J20" t="n">
-        <v>3.054491051432191</v>
+        <v>3.064302875191801</v>
       </c>
       <c r="K20" t="n">
-        <v>50.66531884494529</v>
+        <v>57.4966147269933</v>
       </c>
       <c r="L20" t="n">
-        <v>8.746444560820311</v>
+        <v>9.209178135260879</v>
       </c>
       <c r="M20" t="n">
-        <v>99.983629706087</v>
+        <v>99.98151372487303</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>46.97436332450452</v>
+        <v>39.99652633360476</v>
       </c>
       <c r="C21" t="n">
-        <v>38.29324774332291</v>
+        <v>30.86040070988186</v>
       </c>
       <c r="D21" t="n">
-        <v>3.204221755697855</v>
+        <v>2.472404972565319</v>
       </c>
       <c r="E21" t="n">
-        <v>10.90340428573855</v>
+        <v>8.570353003494809</v>
       </c>
       <c r="F21" t="n">
-        <v>3.055378664120707</v>
+        <v>3.065484103622609</v>
       </c>
       <c r="G21" t="n">
-        <v>21.14137077459957</v>
+        <v>16.76405470711756</v>
       </c>
       <c r="H21" t="n">
-        <v>5.205097020396828</v>
+        <v>5.59620923873558</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4095121598303075</v>
+        <v>0.46253620444628</v>
       </c>
       <c r="J21" t="n">
-        <v>3.055378664120707</v>
+        <v>3.065484103622609</v>
       </c>
       <c r="K21" t="n">
-        <v>53.02563667549548</v>
+        <v>60.00347366639524</v>
       </c>
       <c r="L21" t="n">
-        <v>8.667469141409221</v>
+        <v>9.120713691237913</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9863535602276</v>
+        <v>99.98458806751501</v>
       </c>
     </row>
     <row r="22">
@@ -1320,40 +1320,40 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>44.66576396301407</v>
+        <v>37.67392825358754</v>
       </c>
       <c r="C22" t="n">
-        <v>36.05265280753154</v>
+        <v>28.6139398462895</v>
       </c>
       <c r="D22" t="n">
-        <v>2.991923048994055</v>
+        <v>2.26430500568196</v>
       </c>
       <c r="E22" t="n">
-        <v>10.2731273805244</v>
+        <v>7.939826472730224</v>
       </c>
       <c r="F22" t="n">
-        <v>3.056156996674327</v>
+        <v>3.066529905770722</v>
       </c>
       <c r="G22" t="n">
-        <v>19.74062949774763</v>
+        <v>15.35304022199368</v>
       </c>
       <c r="H22" t="n">
-        <v>5.206422975998762</v>
+        <v>5.598118407873414</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3413470664005739</v>
+        <v>0.3855783337668262</v>
       </c>
       <c r="J22" t="n">
-        <v>3.056156996674327</v>
+        <v>3.066529905770722</v>
       </c>
       <c r="K22" t="n">
-        <v>55.33423603698593</v>
+        <v>62.32607174641245</v>
       </c>
       <c r="L22" t="n">
-        <v>8.601735817709459</v>
+        <v>9.047140179396756</v>
       </c>
       <c r="M22" t="n">
-        <v>99.98862466222693</v>
+        <v>99.98715177209871</v>
       </c>
     </row>
     <row r="23">
@@ -1361,40 +1361,40 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>42.75676536958319</v>
+        <v>35.66340617438444</v>
       </c>
       <c r="C23" t="n">
-        <v>34.20024764528739</v>
+        <v>26.66673207332998</v>
       </c>
       <c r="D23" t="n">
-        <v>2.816104194385745</v>
+        <v>2.083518743682347</v>
       </c>
       <c r="E23" t="n">
-        <v>9.754313264607712</v>
+        <v>7.396547866134266</v>
       </c>
       <c r="F23" t="n">
-        <v>3.056834889149264</v>
+        <v>3.067451129155764</v>
       </c>
       <c r="G23" t="n">
-        <v>18.58058132448062</v>
+        <v>14.12722534939528</v>
       </c>
       <c r="H23" t="n">
-        <v>5.207577823397181</v>
+        <v>5.599800151651572</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2845189844134003</v>
+        <v>0.3214118052094528</v>
       </c>
       <c r="J23" t="n">
-        <v>3.056834889149264</v>
+        <v>3.067451129155764</v>
       </c>
       <c r="K23" t="n">
-        <v>57.24323463041681</v>
+        <v>64.33659382561555</v>
       </c>
       <c r="L23" t="n">
-        <v>8.547035861340234</v>
+        <v>8.985963591783158</v>
       </c>
       <c r="M23" t="n">
-        <v>99.99051813704443</v>
+        <v>99.98928949072869</v>
       </c>
     </row>
     <row r="24">
@@ -1402,40 +1402,40 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>40.48485391980044</v>
+        <v>33.47581709291996</v>
       </c>
       <c r="C24" t="n">
-        <v>31.97543874845356</v>
+        <v>24.53179453540448</v>
       </c>
       <c r="D24" t="n">
-        <v>2.607944033776324</v>
+        <v>1.887424678551657</v>
       </c>
       <c r="E24" t="n">
-        <v>9.109160246111365</v>
+        <v>6.785028405147064</v>
       </c>
       <c r="F24" t="n">
-        <v>3.057431749793939</v>
+        <v>3.068269446266803</v>
       </c>
       <c r="G24" t="n">
-        <v>17.20714606578845</v>
+        <v>12.79761645762012</v>
       </c>
       <c r="H24" t="n">
-        <v>5.208594626191437</v>
+        <v>5.601294034386636</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2371454483449805</v>
+        <v>0.2679146246808723</v>
       </c>
       <c r="J24" t="n">
-        <v>3.057431749793939</v>
+        <v>3.068269446266803</v>
       </c>
       <c r="K24" t="n">
-        <v>59.51514608019956</v>
+        <v>66.52418290708005</v>
       </c>
       <c r="L24" t="n">
-        <v>8.501511866224279</v>
+        <v>8.935094451815214</v>
       </c>
       <c r="M24" t="n">
-        <v>99.9920966948774</v>
+        <v>99.99107189429974</v>
       </c>
     </row>
     <row r="25">
@@ -1443,40 +1443,40 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>39.10593036432353</v>
+        <v>32.04824257236695</v>
       </c>
       <c r="C25" t="n">
-        <v>30.63569540781887</v>
+        <v>23.14797483157166</v>
       </c>
       <c r="D25" t="n">
-        <v>2.453765919721012</v>
+        <v>1.756489359831066</v>
       </c>
       <c r="E25" t="n">
-        <v>8.939261136224966</v>
+        <v>6.418065763651012</v>
       </c>
       <c r="F25" t="n">
-        <v>3.057946859346818</v>
+        <v>3.068982109014423</v>
       </c>
       <c r="G25" t="n">
-        <v>16.18988292887365</v>
+        <v>11.90981414752835</v>
       </c>
       <c r="H25" t="n">
-        <v>5.209472159058427</v>
+        <v>5.602595039290761</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1976545017518381</v>
+        <v>0.2233140440369194</v>
       </c>
       <c r="J25" t="n">
-        <v>3.057946859346818</v>
+        <v>3.068982109014423</v>
       </c>
       <c r="K25" t="n">
-        <v>60.89406963567647</v>
+        <v>67.95175742763304</v>
       </c>
       <c r="L25" t="n">
-        <v>8.463647582939526</v>
+        <v>8.8928256678875</v>
       </c>
       <c r="M25" t="n">
-        <v>99.99341262643486</v>
+        <v>99.99255792709221</v>
       </c>
     </row>
     <row r="26">
@@ -1484,40 +1484,40 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>37.23294227668443</v>
+        <v>30.26955270651192</v>
       </c>
       <c r="C26" t="n">
-        <v>28.79532077065954</v>
+        <v>21.40567735361938</v>
       </c>
       <c r="D26" t="n">
-        <v>2.284096857382123</v>
+        <v>1.597557393022119</v>
       </c>
       <c r="E26" t="n">
-        <v>8.386661946670955</v>
+        <v>5.910714825412649</v>
       </c>
       <c r="F26" t="n">
-        <v>3.058397853417982</v>
+        <v>3.069611167316415</v>
       </c>
       <c r="G26" t="n">
-        <v>15.07041092307177</v>
+        <v>10.83218155260175</v>
       </c>
       <c r="H26" t="n">
-        <v>5.210240465757561</v>
+        <v>5.60374341969735</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1647363769660542</v>
+        <v>0.1861331811452125</v>
       </c>
       <c r="J26" t="n">
-        <v>3.058397853417982</v>
+        <v>3.069611167316415</v>
       </c>
       <c r="K26" t="n">
-        <v>62.76705772331557</v>
+        <v>69.73044729348808</v>
       </c>
       <c r="L26" t="n">
-        <v>8.432131103198442</v>
+        <v>8.857672185002617</v>
       </c>
       <c r="M26" t="n">
-        <v>99.99450959717356</v>
+        <v>99.99379683211008</v>
       </c>
     </row>
     <row r="27">
@@ -1525,40 +1525,40 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>35.71745761554678</v>
+        <v>28.85822918784985</v>
       </c>
       <c r="C27" t="n">
-        <v>27.3069629717616</v>
+        <v>20.02459325040547</v>
       </c>
       <c r="D27" t="n">
-        <v>2.133543365092766</v>
+        <v>1.470971640345865</v>
       </c>
       <c r="E27" t="n">
-        <v>8.041065857535926</v>
+        <v>5.513177393944252</v>
       </c>
       <c r="F27" t="n">
-        <v>3.058789736121744</v>
+        <v>3.070161230786272</v>
       </c>
       <c r="G27" t="n">
-        <v>14.0770629451298</v>
+        <v>9.973871321650986</v>
       </c>
       <c r="H27" t="n">
-        <v>5.210908071222524</v>
+        <v>5.604747590708469</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1372979043222775</v>
+        <v>0.1551387796277315</v>
       </c>
       <c r="J27" t="n">
-        <v>3.058789736121744</v>
+        <v>3.070161230786272</v>
       </c>
       <c r="K27" t="n">
-        <v>64.28254238445321</v>
+        <v>71.14177081215016</v>
       </c>
       <c r="L27" t="n">
-        <v>8.405918633313922</v>
+        <v>8.828465571301443</v>
       </c>
       <c r="M27" t="n">
-        <v>99.99542398952873</v>
+        <v>99.99482963385708</v>
       </c>
     </row>
     <row r="28">
@@ -1566,40 +1566,40 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>34.66703665938793</v>
+        <v>27.86993683142787</v>
       </c>
       <c r="C28" t="n">
-        <v>26.27911010109947</v>
+        <v>19.06143628303147</v>
       </c>
       <c r="D28" t="n">
-        <v>2.004151256071358</v>
+        <v>1.365508871945032</v>
       </c>
       <c r="E28" t="n">
-        <v>7.995386714279507</v>
+        <v>5.369454485467192</v>
       </c>
       <c r="F28" t="n">
-        <v>3.059126280308174</v>
+        <v>3.070636030258167</v>
       </c>
       <c r="G28" t="n">
-        <v>13.22333721679511</v>
+        <v>9.258784740506796</v>
       </c>
       <c r="H28" t="n">
-        <v>5.211481402823805</v>
+        <v>5.605614363166374</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1144275088018013</v>
+        <v>0.1293023098261395</v>
       </c>
       <c r="J28" t="n">
-        <v>3.059126280308174</v>
+        <v>3.070636030258167</v>
       </c>
       <c r="K28" t="n">
-        <v>65.33296334061207</v>
+        <v>72.13006316857214</v>
       </c>
       <c r="L28" t="n">
-        <v>8.384112727612832</v>
+        <v>8.804191137851184</v>
       </c>
       <c r="M28" t="n">
-        <v>99.99618616932437</v>
+        <v>99.9956905894548</v>
       </c>
     </row>
   </sheetData>
